--- a/AAII_Financials/Quarterly/AVY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AVY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>AVY</t>
   </si>
@@ -656,540 +656,553 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44198</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2462900</v>
+      </c>
+      <c r="E8" s="3">
         <v>2298500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2271200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2215500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2220500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2148300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2185700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2183400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2235300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2151300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2110500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2098300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2090500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2065000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2025900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2317100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2347000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2349300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2183200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2071800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2102000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2051300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1990900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1729100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1528500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1723000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1772900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1761400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1795700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1740100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1768700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1759700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1854200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1776400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1735300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1679500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1626900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1572100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1550800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1508700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1733500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1633700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1620500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1580500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1581400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1526800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1576500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1556800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1572600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1519100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1514500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1512500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1537100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1522700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1525700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1697900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1703500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1708000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1598100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1517400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1525700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1454300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1419800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1244900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1145600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1237900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1288200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1289700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1313400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1274700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1297200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1300500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1352800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1293000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1269700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1227900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1174300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1129700</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1125400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1091100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>729400</v>
+      </c>
+      <c r="E10" s="3">
         <v>664800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>650700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>635000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>639100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>621500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>609200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>626600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>662700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>632200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>596000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>585800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>553400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>542300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>500200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>619200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>643500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>641300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>585100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>554400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>576300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>597000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>571100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>484200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>382900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>485100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>484700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>471700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>482300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>465400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>471500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>459200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>501400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>483400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>465600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>451600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>452600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>442400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>425400</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>417600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,19 +1245,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3">
         <v>136600</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>24</v>
@@ -1252,11 +1266,11 @@
       <c r="H12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="3">
         <v>137800</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>24</v>
@@ -1264,11 +1278,11 @@
       <c r="L12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12" s="3">
         <v>135800</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>24</v>
@@ -1312,50 +1326,53 @@
       <c r="AB12" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AC12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD12" s="3">
         <v>21400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>21700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>24800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>24700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>23700</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>24500</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>25200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>24800</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>23400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>23600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>23500</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>22900</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>22300</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,175 +1493,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E14" s="3">
         <v>17100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>36100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>12800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>19200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>16000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>14900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>22600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>54100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>64300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>17600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>21800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>3700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>10900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>40000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>4900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>28600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>6700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>457700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>59400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>13200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>11100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>10800</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>10200</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>6500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>6200</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>86400</v>
+      </c>
+      <c r="E15" s="3">
         <v>86800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>45300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>84000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>80800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>77900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>45100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>78100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>78600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>77300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>49100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>75100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>74000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>72300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1720,8 +1743,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1787,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>2128300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2008800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1982600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1934400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1933800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1873800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1877200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1903700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1946500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1884300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1847200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1837300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1856700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1857100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1862000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2046000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2060400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2081000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1939700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1848300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1848100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1783700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1733500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1531200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1425000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1542600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1607700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1580700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1606100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2025000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1591000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1582700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1711700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1614000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1578000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1532700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1477400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1436200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1424500</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1380700</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>334600</v>
+      </c>
+      <c r="E18" s="3">
         <v>289700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>288600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>281100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>286700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>274500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>308500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>279700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>288800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>267000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>263300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>261000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>233800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>207900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>163900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>271100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>286600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>268300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>243500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>223500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>253900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>267600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>257400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>197900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>103500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>180400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>165200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>180700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>189600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-284900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>177700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>177000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>142500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>162400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>157300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>146800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>149500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>135900</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>126300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>128000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,113 +2082,114 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>21900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>22400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-89900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AK20" s="3">
-        <v>0</v>
-      </c>
       <c r="AL20" s="3">
         <v>0</v>
       </c>
@@ -2171,175 +2205,181 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>425300</v>
+      </c>
+      <c r="E21" s="3">
         <v>379900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>326400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>364900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>369000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>355000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>331700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>362300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>368800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>341600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>290000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>344800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>310400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>284600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>242700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>344500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>361100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>341700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>316600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>286300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>310500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>323300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>310800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>249800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>153600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>228400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>210900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>223900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>233600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-239900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>132800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>214700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>184700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>203600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>201200</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>190800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>195700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>180500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>170900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>174100</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E22" s="3">
         <v>35600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>37200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>33300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>30900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>29700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>31900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26400</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2415,252 +2455,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>282700</v>
+      </c>
+      <c r="E23" s="3">
         <v>240400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>207800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>234800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>255500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>227000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>241400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>239300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>238400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>234400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>201600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>184600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>140200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>168300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>169200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>272500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>287900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>269700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>244000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>224400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>255300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>268900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>255300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>197800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>103300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>180900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>165300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>179900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>188700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-284400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>87800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>168000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>139900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>159100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>157300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>146800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>149500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>135900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>126300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>128000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>78600</v>
+      </c>
+      <c r="E24" s="3">
         <v>72300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>68500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>66500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>60700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>67400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>57600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>61600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>58500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>46300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>39800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>47100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>46300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>51000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>73400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>71500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>60900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>59200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>70400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>58100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>62900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>46300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>22200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>46300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>34600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>44900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-138400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-10400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>16400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>41300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>34500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>44900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>38500</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>28600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>23700</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>64300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2781,252 +2830,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>204100</v>
+      </c>
+      <c r="E26" s="3">
         <v>168100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>166400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>166300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>189000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>166300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>174000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>181700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>176800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>172400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>143100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>138300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>100400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>121200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>122900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>221500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>214500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>198200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>183100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>165200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>184900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>210800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>192400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>151500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>81100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>134600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>163100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>145300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>143800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-146000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>98200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>151600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>98600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>124600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>112400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>108300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>120900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>112200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>62000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>204100</v>
+      </c>
+      <c r="E27" s="3">
         <v>168100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>166400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>166300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>189000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>166300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>174000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>181700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>176800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>172400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>143100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>138300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>100400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>121200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>122900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>221500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>214500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>198200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>182700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>164100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>183800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>209500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>191500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>150500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>79700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>134200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>162500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>144600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>143400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-146900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>98000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>150800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>98200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>124000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>112400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>108300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>120900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>112200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>62000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3147,8 +3205,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3221,17 +3282,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -3239,23 +3300,23 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-900</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>1200</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-172000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3263,14 +3324,17 @@
       <c r="AN29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
+      <c r="AO29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3391,8 +3455,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3513,113 +3580,116 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-21900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-22400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>89900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>9000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3300</v>
       </c>
-      <c r="AK32" s="3">
-        <v>0</v>
-      </c>
       <c r="AL32" s="3">
         <v>0</v>
       </c>
@@ -3635,130 +3705,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>204100</v>
+      </c>
+      <c r="E33" s="3">
         <v>168100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>166400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>166300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>189000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>166300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>174000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>181700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>176800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>172400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>143100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>138300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>100400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>121200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>122900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>221500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>214500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>198200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>182700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>164100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>183800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>209500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>191500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>150500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>79700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>134200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>162500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>144600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>143400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-146900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>97100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>149500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>95600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>125200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-59600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>108300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>120900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>112200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>62000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3879,257 +3955,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>204100</v>
+      </c>
+      <c r="E35" s="3">
         <v>168100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>166400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>166300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>189000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>166300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>174000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>181700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>176800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>172400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>143100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>138300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>100400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>121200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>122900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>221500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>214500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>198200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>182700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>164100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>183800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>209500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>191500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>150500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>79700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>134200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>162500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>144600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>143400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-146900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>97100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>149500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>95600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>125200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-59600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>108300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>120900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>112200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>62000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44198</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4172,8 +4257,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4216,175 +4302,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>227300</v>
+      </c>
+      <c r="E41" s="3">
         <v>255100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>202800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>536300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>215900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>195900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>329100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>212700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>208800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>185700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>215000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>209900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>217100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>351300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>167200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>128200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>164800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>147100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>162700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>207200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>344800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>328000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>252300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>284700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>262600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>742000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>253700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>224200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>247300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>225700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>232000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>217600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>215800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>187500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>224400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>232300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>209400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>294900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>195100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>189400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E42" s="3">
         <v>46600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>46900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>45400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>39800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>38800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>38100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>37900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>36000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>35100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>34000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>35500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>35200</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4460,540 +4550,555 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1793500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1647100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1503900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1627800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1626500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1518000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1466200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1574700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1528600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1478000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1414900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1426200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1415200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1369100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1374400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1585600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1565100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1551400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1424500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1441200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1338900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1301400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1235200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1212700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1114600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1222500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1212200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1224200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1232000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1198700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1216700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1235700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1236200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1240000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1209200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1184800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1138100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1099500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1031300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1069700</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1031700</v>
+      </c>
+      <c r="E44" s="3">
         <v>989400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>975800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1037400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1026900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1017500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>978100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1013500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>979900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>972500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>920700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>936100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>990500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1050600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1009900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1014400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>990100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>960900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>907200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>879100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>824800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>786700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>717200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>662600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>726600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>723300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>663000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>665000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>671000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>688300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>651400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>682500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>660800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>678200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>609600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>620000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>618500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>579900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>519100</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>565300</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300600</v>
+      </c>
+      <c r="E45" s="3">
         <v>281300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>260900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>276800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>274700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>260200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>267200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>245900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>214300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>214600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>210300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>208100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>192700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>183000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>230500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>233600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>228800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>234900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>240200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>251000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>233100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>216300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>211500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>214500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>220800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>225800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>211700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>220000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>226900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>211000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>197900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>223000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>215300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>226600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>194700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>246200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>243800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>210300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>159300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>189200</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3400500</v>
+      </c>
+      <c r="E46" s="3">
         <v>3219500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2990300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3523700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3183800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3030400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3078700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3084700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2967800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2886800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2796000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2814300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2851000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2989200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2782000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2961800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2948800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2894300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2734600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2778500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2741600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2632400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2416200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2374500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2324600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2913600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2340600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2333400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2377200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2323700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2298000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2358800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2328100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2332300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2237900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2283300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2209800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2184600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1904800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2013600</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>132700</v>
+      </c>
+      <c r="E47" s="3">
         <v>57700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>59100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>61300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>62400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>53400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>52900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>54400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>68000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>71000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>82800</v>
-      </c>
-      <c r="O47" s="3">
-        <v>71000</v>
       </c>
       <c r="P47" s="3">
         <v>71000</v>
       </c>
       <c r="Q47" s="3">
-        <v>0</v>
+        <v>71000</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5025,35 +5130,35 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>8800</v>
       </c>
       <c r="AD47" s="3">
         <v>8800</v>
       </c>
       <c r="AE47" s="3">
+        <v>8800</v>
+      </c>
+      <c r="AF47" s="3">
         <v>9800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>10500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>7200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>9000</v>
-      </c>
-      <c r="AK47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AL47" s="3" t="s">
         <v>24</v>
@@ -5070,252 +5175,261 @@
       <c r="AP47" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ47" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1565100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1573500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1823500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1579900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1604200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1583000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1814200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1612300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1590000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1598200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1826000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1555200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1567000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1565600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1540200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1442600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1451000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1477500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1477700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1405500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1344800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1329000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1343700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1233900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1228800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1232000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1348800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1285400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1290900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1296400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1137400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1086900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1084500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1117600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1097900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1047000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1017800</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>940300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>915200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>905400</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3038200</v>
+      </c>
+      <c r="E49" s="3">
         <v>3064200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3322300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2723900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2744600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2726100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2921400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2795900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2790700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2817500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3017600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2836600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2868900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2720600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2702700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2679900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2738600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2800800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2792900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2828200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1361700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1363500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1361300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1253400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1235300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1225700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1057300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1049500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1077100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1077800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1085800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1101700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1109700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1172300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1151400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1147200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1118500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>909800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>860300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>892500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5436,8 +5550,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5558,130 +5675,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>936000</v>
+      </c>
+      <c r="E52" s="3">
         <v>921300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>481200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>845800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>841600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>889100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>426500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>795200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>782300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>769200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>383500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>729000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>788700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>757600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>925600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>958000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>954000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>966200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>966400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>955500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>974400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>948300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>962700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>859000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>863000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>889600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>733300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>661600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>634700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>645300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>649600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>627300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>632800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>649300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>649700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>792500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>745700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>731200</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>716100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>788900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5802,130 +5925,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9212300</v>
+      </c>
+      <c r="E54" s="3">
         <v>8978600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8801700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8866900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>8568200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8354700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8404200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8451900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8298200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8255200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8209800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8133100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8266300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8222300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>7950500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8042300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8092400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8138800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7971600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7967700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6422500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6273200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6083900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5720800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5651700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6260900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5488800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5338700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5389700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5353700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5177500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5181900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5163100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>5280500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5136900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5270000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>5091800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4765900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>4396400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>4600400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5968,8 +6097,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6012,635 +6142,651 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1524700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1329500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1261700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1303200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1307500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1272600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1340700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1343200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1313400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1301500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1277100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1265300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1234800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1236200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1339300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1383100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1410900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1372500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1298800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1268200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1226500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1178000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1050900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>932800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>956500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1030800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1066100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1041200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1055400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1033700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1030500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1048000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1034400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1064400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1007200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>949200</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>930900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>906100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>841900</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>866700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>500500</v>
+      </c>
+      <c r="E58" s="3">
         <v>605000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>576000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>578800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>922000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>877500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>641900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1116800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1172300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1170500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>667600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>716000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>635800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>648300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>598600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>669900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>738600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>494900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>318800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>398800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>33600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>116900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>64700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>124100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>268600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>832300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>440200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>514200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>558500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>350300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>194600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>571700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>384300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>370300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>265400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>383000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>444000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>333200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>579100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>587600</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>732000</v>
+      </c>
+      <c r="E59" s="3">
         <v>663000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>411400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>657700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>622300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>604900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>428200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>606000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>568100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>623800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>388000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>552000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>549200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>560200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>861900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>886300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>851000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>855800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>930300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>942400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>822400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>763600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>810400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>759100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>684400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>697000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>747500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>712500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>664600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>656500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>768900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>738500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>690500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>646700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>699200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>691100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>597500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>520000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>583300</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>601800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3005000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2799700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2653600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2787100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3062100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2952800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2862600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3349000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3300200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3308200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2699500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2744300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2608700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2643700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2799800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2939300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3000500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2723200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2547900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2609400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2082500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2058500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1926000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1816000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1909500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2560100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2253800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2267900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2278500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2040500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1994000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2358200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2109200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2081400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1971800</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2023300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1972400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1759300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2004300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2056100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3185100</v>
+        <v>3184700</v>
       </c>
       <c r="E61" s="3">
+        <v>3185800</v>
+      </c>
+      <c r="F61" s="3">
         <v>3377600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3202300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2628200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2581600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2736000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2042100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2046500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2069900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2774400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2597600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2909700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2910800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2503500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2462900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2493400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2773800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2785900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2800200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2020200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2025900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2052100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2020000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1997600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1988000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1499300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1483700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1503300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1759900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1771600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1295300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1289700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1342700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1316300</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1298400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1276300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1250200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>713400</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>713000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E62" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>12700</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>24</v>
@@ -6666,86 +6812,89 @@
       <c r="P62" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R62" s="3">
         <v>615000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>632800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>661600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>709300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>713400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>758900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>616200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>606900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>620900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>550200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>530700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>539400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>531700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>529700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>545400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>561400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>456800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>481300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>742300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>766700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>802600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>813400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>773300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>741800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>753200</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>788900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6866,8 +7015,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6988,8 +7140,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7110,130 +7265,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6889500</v>
+      </c>
+      <c r="E66" s="3">
         <v>6678100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6559600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6655900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6366600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6184200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6091900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6058000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6011100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6051200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6081900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6069500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6251100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6179400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5918300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6035000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6155500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6206300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6047200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6168500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4718900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4691300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4599000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4386200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4437800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5087500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>4284800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4281300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4327200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4361800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4222400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4134800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4141200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4190800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4090700</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4135100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4022000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3751300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>3470900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>3558000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7276,8 +7437,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7398,8 +7560,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7520,8 +7685,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7642,8 +7810,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7764,130 +7935,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5844000</v>
+      </c>
+      <c r="E72" s="3">
         <v>5709400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5597500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5498300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5399300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5276500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5151200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5042700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4922200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4809100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4691800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4608200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4526900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4486400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4414600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4347000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4182000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4023200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3880700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3749700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3637300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3504400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3349300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3205500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3100200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3064800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2979100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2861700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2762300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>2663500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2864900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2809400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2702100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2647800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2596700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2693300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2621800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2537900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2473300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2444100</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8008,8 +8185,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8130,8 +8310,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8252,130 +8435,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2322800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2300500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2242100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2211000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2201600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2170500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2312300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2393900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2287100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2204000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2127900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2063600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2015200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2042900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2032200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2007300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1936900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1932500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1924400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>1799200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1703600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1581900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1484900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1334600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1213900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1173400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1204000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1057400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1062500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>991900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>955100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1047100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1021900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1089700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1046200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1134900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1069800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1014600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>925500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1042400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8496,257 +8685,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44198</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>204100</v>
+      </c>
+      <c r="E81" s="3">
         <v>168100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>166400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>166300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>189000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>166300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>174000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>181700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>176800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>172400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>143100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>138300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>100400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>121200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>122900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>221500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>214500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>198200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>182700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>164100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>183800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>209500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>191500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>150500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>79700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>134200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>162500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>144600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>143400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-146900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>97100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>149500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>95600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>125200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-59600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>108300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>120900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>112200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>62000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>89100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8789,130 +8987,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E83" s="3">
         <v>48800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>45100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>48800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>49700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>49000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>48900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>47000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>46700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>44800</v>
-      </c>
-      <c r="M83" s="3">
-        <v>44000</v>
       </c>
       <c r="N83" s="3">
         <v>44000</v>
       </c>
       <c r="O83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="P83" s="3">
         <v>44400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>73500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>72000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>73200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>72000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>72600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>61900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>55200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>54400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>55500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>52000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>50300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>47500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>45600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>44000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>44900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>44500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>45000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>46700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>44800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>44500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>43900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>44000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>46200</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>44600</v>
       </c>
       <c r="AO83" s="3">
         <v>44600</v>
       </c>
       <c r="AP83" s="3">
+        <v>44600</v>
+      </c>
+      <c r="AQ83" s="3">
         <v>46100</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9033,8 +9235,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9155,8 +9360,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9277,8 +9485,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9399,8 +9610,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9521,130 +9735,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>408200</v>
+      </c>
+      <c r="E89" s="3">
         <v>136500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>376800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>312100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>208800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>351200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>270100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>197700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>119800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>311900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>322600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>189600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>345800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>220800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>268200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>126200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>284000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>286000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>267500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>209300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>309500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>257800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>179600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>279500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>228200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>203400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>35400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>270200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-21800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>193500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>16000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>257500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>214300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>163000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>15300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>219600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>149700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9687,130 +9907,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-28300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-67100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-35900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-30000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-69500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-43000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-47500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-48800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-92300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-57100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-51400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-64500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-101400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-80400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-61400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-55300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-131700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-50200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-58600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-109700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-30700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-33200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-86500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-53100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-38000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-41800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-94000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-53200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-43900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-35600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-79100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-44900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-36200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-85100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-54100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9931,8 +10155,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10053,130 +10280,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-117800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-32600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-491400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-43400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-28000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-33200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-73600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-50700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-56800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-114800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-205300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-116600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-102700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-80400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-63000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-86600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-132200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1489800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-64700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-51200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-191300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-34900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-42400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-285600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-95400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-68000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-45600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-42000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-105100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-45300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-46300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-35800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-57200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-274200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-112000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-89900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-281300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10219,79 +10452,80 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>76200</v>
+      </c>
+      <c r="E96" s="3">
         <v>72300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>72400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>73100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>73500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>69400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>70400</v>
-      </c>
-      <c r="J96" s="3">
-        <v>70900</v>
       </c>
       <c r="K96" s="3">
         <v>70900</v>
       </c>
       <c r="L96" s="3">
+        <v>70900</v>
+      </c>
+      <c r="M96" s="3">
         <v>65300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>65200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>65300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>65400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>60800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-60600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-60900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-61200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-56200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-56300</v>
       </c>
       <c r="V96" s="3">
         <v>-56300</v>
       </c>
       <c r="W96" s="3">
+        <v>-56300</v>
+      </c>
+      <c r="X96" s="3">
         <v>-56400</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-51600</v>
       </c>
       <c r="Y96" s="3">
         <v>-51600</v>
       </c>
       <c r="Z96" s="3">
-        <v>-48400</v>
+        <v>-51600</v>
       </c>
       <c r="AA96" s="3">
         <v>-48400</v>
@@ -10303,46 +10537,49 @@
         <v>-48400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-48400</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-48600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-48800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-43900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-44400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-45300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-45700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-39600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-39700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-39600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-39800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-36400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-36300</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-36600</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10463,8 +10700,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10585,8 +10825,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10707,370 +10950,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-319000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-50600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-219300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>52900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-163600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-84900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-156300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-217700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-117100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-85000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-194500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-305800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-116700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>299800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-204700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-172800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-182600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-55100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-195800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1067700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-187400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-80200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-158000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-205800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-617600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>773700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-156900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-178500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-134200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-150200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>73900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-110000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-21800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-164700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-135800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>21900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>194700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-117600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>104700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E101" s="3">
         <v>1200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>2500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>4700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>4300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>3800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="E102" s="3">
         <v>52300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-333500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>320400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-133200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>116400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>23100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-29300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-7200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-134200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>184100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-36600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>17700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-15600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-44500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-137600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>16800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>75700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-32400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-479400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>488300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>29500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-23100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>21600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>14400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>28300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-36900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-7900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>22900</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-85500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>99800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>5700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-26700</v>
       </c>
     </row>
